--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_IBERSOL CB TARRAGONA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_IBERSOL CB TARRAGONA.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0904</v>
+        <v>4.2339</v>
       </c>
       <c r="E2" t="n">
-        <v>8.777200000000001</v>
+        <v>9.270899999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.6867</v>
+        <v>-5.037</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1798</v>
+        <v>2.2124</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3531</v>
+        <v>5.4009</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.1733</v>
+        <v>-3.1885</v>
       </c>
       <c r="J2" t="n">
-        <v>6.9237</v>
+        <v>7.1755</v>
       </c>
       <c r="K2" t="n">
-        <v>6.918</v>
+        <v>7.1021</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0057</v>
+        <v>0.0733</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.744</v>
+        <v>-4.963</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.565</v>
+        <v>-1.7012</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.179</v>
+        <v>-3.2618</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0518</v>
+        <v>0.0525</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6044</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6563</v>
+        <v>0.6155</v>
       </c>
       <c r="V2" t="n">
-        <v>3.2592</v>
+        <v>3.3321</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6588</v>
+        <v>5.7742</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3995</v>
+        <v>-2.4421</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6006</v>
+        <v>0.5535</v>
       </c>
       <c r="E3" t="n">
-        <v>1.335</v>
+        <v>1.4022</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7343</v>
+        <v>-0.8487</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5416</v>
+        <v>-0.5887</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7572</v>
+        <v>-0.8026</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2156</v>
+        <v>0.214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7798</v>
+        <v>0.7995</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6998</v>
+        <v>0.7184</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3214</v>
+        <v>-1.3881</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.457</v>
+        <v>-1.521</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5424</v>
+        <v>0.5316</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3557</v>
+        <v>0.3553</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1867</v>
+        <v>0.1763</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5999</v>
+        <v>0.6105</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. KOHAN LOPEZ</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2894</v>
+        <v>-0.3002</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0445</v>
+        <v>1.7136</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2449</v>
+        <v>-2.0138</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2443</v>
+        <v>-0.1422</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2443</v>
+        <v>-0.5594</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.4172</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02</v>
+        <v>2.3616</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02</v>
+        <v>-0.5003</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.8619</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2643</v>
+        <v>-2.5038</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2643</v>
+        <v>-0.0591</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-2.4447</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.7526</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.7526</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0451</v>
+        <v>-1.5796</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0645</v>
+        <v>-0.9275</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0193</v>
+        <v>-0.6521</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.3311</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>T. KOHAN LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.344</v>
+        <v>-0.3004</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4659</v>
+        <v>-0.0413</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8099</v>
+        <v>-0.2591</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1784</v>
+        <v>-0.2571</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4835</v>
+        <v>-0.2571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3051</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.173</v>
+        <v>0.0205</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.518</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
-        <v>2.691</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3514</v>
+        <v>-0.2776</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0346</v>
+        <v>-0.2776</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3859</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8005</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8005</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.626</v>
+        <v>-0.0433</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9669</v>
+        <v>-0.0618</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6591</v>
+        <v>0.0186</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3401</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1051</v>
+        <v>-1.13</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1316</v>
+        <v>-0.0916</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9735</v>
+        <v>-1.0384</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3954</v>
+        <v>-1.4113</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6824</v>
+        <v>-0.6753</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.713</v>
+        <v>-0.736</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0618</v>
+        <v>0.0939</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0182</v>
+        <v>0.0129</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4572</v>
+        <v>-1.5052</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6642</v>
+        <v>-0.6882</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.793</v>
+        <v>-0.8171</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2001</v>
+        <v>-0.1947</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2903</v>
+        <v>0.2813</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0067</v>
+        <v>0.0092</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2836</v>
+        <v>0.2721</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.197</v>
+        <v>-1.1893</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.07290000000000001</v>
+        <v>0.1014</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1241</v>
+        <v>-1.2906</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0129</v>
+        <v>-2.046</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2178</v>
+        <v>1.2187</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.2308</v>
+        <v>-3.2648</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8234</v>
+        <v>0.9052</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2614</v>
+        <v>1.3266</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.438</v>
+        <v>-0.4213</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8363</v>
+        <v>-2.9512</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0436</v>
+        <v>-0.1078</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.7927</v>
+        <v>-2.8434</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2638</v>
+        <v>-0.2474</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1046</v>
+        <v>0.1172</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3684</v>
+        <v>-0.3647</v>
       </c>
       <c r="V7" t="n">
-        <v>1.88</v>
+        <v>1.8832</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6802</v>
+        <v>0.6621</v>
       </c>
     </row>
     <row r="8">
@@ -1033,55 +1033,55 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4728</v>
+        <v>-1.5218</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0089</v>
+        <v>-0.0021</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4638</v>
+        <v>-1.5197</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.744</v>
+        <v>-1.7876</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1997</v>
+        <v>-1.2316</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5443</v>
+        <v>-0.556</v>
       </c>
       <c r="J8" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8639</v>
+        <v>-1.9092</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1997</v>
+        <v>-1.2316</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6643</v>
+        <v>-0.6776</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1289</v>
+        <v>-0.1237</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1289</v>
+        <v>-0.1237</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9836</v>
+        <v>-1.9768</v>
       </c>
       <c r="E9" t="n">
-        <v>2.6985</v>
+        <v>3.0538</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.682</v>
+        <v>-5.0306</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4606</v>
+        <v>-4.4349</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1409</v>
+        <v>-2.0843</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3197</v>
+        <v>-2.3505</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5546</v>
+        <v>0.794</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1691</v>
+        <v>0.0156</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7237</v>
+        <v>0.7784</v>
       </c>
       <c r="M9" t="n">
-        <v>-5.0152</v>
+        <v>-5.2288</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9718</v>
+        <v>-2.0999</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.0434</v>
+        <v>-3.1289</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7571</v>
+        <v>1.7307</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3651</v>
+        <v>1.3687</v>
       </c>
       <c r="U9" t="n">
-        <v>0.392</v>
+        <v>0.362</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="W9" t="n">
-        <v>1.9791</v>
+        <v>2.0595</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3874</v>
+        <v>-2.4283</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7699</v>
+        <v>-2.4568</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3826</v>
+        <v>0.0285</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.6596</v>
+        <v>-5.714</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.056</v>
+        <v>-4.0441</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6036</v>
+        <v>-1.6699</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7865</v>
+        <v>-2.6431</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.0265</v>
+        <v>-2.8863</v>
       </c>
       <c r="L10" t="n">
-        <v>0.24</v>
+        <v>0.2432</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.873</v>
+        <v>-3.0709</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0295</v>
+        <v>-1.1578</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8435</v>
+        <v>-1.9131</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2133</v>
+        <v>3.1221</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3584</v>
+        <v>1.3595</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8549</v>
+        <v>1.7626</v>
       </c>
       <c r="V10" t="n">
-        <v>2.0594</v>
+        <v>2.1111</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5999</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8376</v>
+        <v>-4.8479</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3803</v>
+        <v>-1.1368</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4573</v>
+        <v>-3.7111</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9749</v>
+        <v>-3.0392</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0638</v>
+        <v>-2.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9111</v>
+        <v>-0.9142</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1256</v>
+        <v>0.2054</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1218</v>
+        <v>0.1565</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0038</v>
+        <v>0.0489</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1005</v>
+        <v>-3.2447</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.1855</v>
+        <v>-2.2815</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9149</v>
+        <v>-0.9631</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8005</v>
+        <v>-1.7526</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2779</v>
+        <v>0.275</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0243</v>
+        <v>-0.0064</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3022</v>
+        <v>0.2815</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7194</v>
+        <v>1.78</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0594</v>
+        <v>-2.1111</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5221</v>
+        <v>-6.6168</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5001</v>
+        <v>0.6913</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.0222</v>
+        <v>-7.3081</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0331</v>
+        <v>-2.0679</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6193</v>
+        <v>-2.689</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="J12" t="n">
-        <v>1.7892</v>
+        <v>1.928</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.1761</v>
+        <v>-1.1443</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9653</v>
+        <v>3.0723</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.8223</v>
+        <v>-3.9959</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4432</v>
+        <v>-1.5447</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.3791</v>
+        <v>-2.4513</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2901</v>
+        <v>-1.2489</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2891</v>
+        <v>-1.2367</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.001</v>
+        <v>-0.0122</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.1992</v>
+        <v>-4.2737</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.448</v>
+        <v>-15.5241</v>
       </c>
       <c r="E13" t="n">
-        <v>10.3686</v>
+        <v>12.5046</v>
       </c>
       <c r="F13" t="n">
-        <v>-25.8161</v>
+        <v>-28.0286</v>
       </c>
       <c r="G13" t="n">
-        <v>-19.065</v>
+        <v>-19.2765</v>
       </c>
       <c r="H13" t="n">
-        <v>-7.6762</v>
+        <v>-7.848800000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-11.3889</v>
+        <v>-11.4277</v>
       </c>
       <c r="J13" t="n">
-        <v>10.5846</v>
+        <v>11.7621</v>
       </c>
       <c r="K13" t="n">
-        <v>4.113099999999999</v>
+        <v>4.8217</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4715</v>
+        <v>6.9405</v>
       </c>
       <c r="M13" t="n">
-        <v>-29.6495</v>
+        <v>-31.0384</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.7892</v>
+        <v>-12.6704</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.8602</v>
+        <v>-18.3681</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.0042</v>
+        <v>-14.6052</v>
       </c>
       <c r="R13" t="n">
-        <v>13.0038</v>
+        <v>12.658</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7789</v>
+        <v>2.750300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1124000000000001</v>
+        <v>0.2908000000000004</v>
       </c>
       <c r="U13" t="n">
-        <v>2.6665</v>
+        <v>2.4596</v>
       </c>
       <c r="V13" t="n">
-        <v>2.8388</v>
+        <v>2.9494</v>
       </c>
       <c r="W13" t="n">
-        <v>14.676</v>
+        <v>15.057</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.837</v>
+        <v>-12.1074</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_IBERSOL CB TARRAGONA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_IBERSOL CB TARRAGONA.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2339</v>
+        <v>5.0275</v>
       </c>
       <c r="E2" t="n">
-        <v>9.270899999999999</v>
+        <v>10.0923</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.037</v>
+        <v>-5.0649</v>
       </c>
       <c r="G2" t="n">
         <v>2.2124</v>
@@ -610,13 +610,13 @@
         <v>1.7526</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0525</v>
+        <v>0.8461</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5629999999999999</v>
+        <v>0.2584</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6155</v>
+        <v>0.5877</v>
       </c>
       <c r="V2" t="n">
         <v>3.3321</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5535</v>
+        <v>1.0143</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4022</v>
+        <v>2.6107</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8487</v>
+        <v>-1.5964</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5887</v>
+        <v>-0.1422</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8026</v>
+        <v>-0.5594</v>
       </c>
       <c r="I3" t="n">
-        <v>0.214</v>
+        <v>0.4172</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7995</v>
+        <v>2.3616</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7184</v>
+        <v>-0.5003</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08110000000000001</v>
+        <v>2.8619</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3881</v>
+        <v>-2.5038</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.521</v>
+        <v>-0.0591</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1329</v>
+        <v>-2.4447</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.7526</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9737</v>
+        <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5316</v>
+        <v>-0.2651</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3553</v>
+        <v>-0.0304</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1763</v>
+        <v>-0.2347</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6105</v>
+        <v>-0.3311</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2211</v>
+        <v>0.2795</v>
       </c>
       <c r="X3" t="n">
         <v>-0.6105</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3002</v>
+        <v>0.3541</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7136</v>
+        <v>1.2028</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0138</v>
+        <v>-0.8487</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1422</v>
+        <v>-0.5887</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5594</v>
+        <v>-0.8026</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4172</v>
+        <v>0.214</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3616</v>
+        <v>0.7995</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5003</v>
+        <v>0.7184</v>
       </c>
       <c r="L4" t="n">
-        <v>2.8619</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5038</v>
+        <v>-1.3881</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0591</v>
+        <v>-1.521</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4447</v>
+        <v>0.1329</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7526</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7526</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5796</v>
+        <v>0.3323</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9275</v>
+        <v>0.156</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6521</v>
+        <v>0.1763</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3311</v>
+        <v>0.6105</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
         <v>-0.6105</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3004</v>
+        <v>-0.2726</v>
       </c>
       <c r="E5" t="n">
         <v>-0.0413</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2591</v>
+        <v>-0.2313</v>
       </c>
       <c r="G5" t="n">
         <v>-0.2571</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0433</v>
+        <v>-0.0155</v>
       </c>
       <c r="T5" t="n">
         <v>-0.0618</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0186</v>
+        <v>0.0464</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.13</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0916</v>
+        <v>0.2074</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0384</v>
+        <v>-1.0941</v>
       </c>
       <c r="G6" t="n">
         <v>-1.4113</v>
@@ -922,13 +922,13 @@
         <v>0.1947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2813</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0092</v>
+        <v>0.3083</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2721</v>
+        <v>0.2164</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1893</v>
+        <v>-1.1382</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1014</v>
+        <v>-0.098</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.2906</v>
+        <v>-1.0402</v>
       </c>
       <c r="G7" t="n">
         <v>-2.046</v>
@@ -1000,13 +1000,13 @@
         <v>1.3632</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2474</v>
+        <v>-0.1963</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1172</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3647</v>
+        <v>-0.1142</v>
       </c>
       <c r="V7" t="n">
         <v>1.8832</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9768</v>
+        <v>-3.0933</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0538</v>
+        <v>1.8816</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.0306</v>
+        <v>-4.9749</v>
       </c>
       <c r="G9" t="n">
         <v>-4.4349</v>
@@ -1156,13 +1156,13 @@
         <v>1.9474</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7307</v>
+        <v>0.6142</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3687</v>
+        <v>0.1966</v>
       </c>
       <c r="U9" t="n">
-        <v>0.362</v>
+        <v>0.4176</v>
       </c>
       <c r="V9" t="n">
         <v>-0.0516</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4283</v>
+        <v>-4.1918</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4568</v>
+        <v>-3.3299</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0285</v>
+        <v>-0.8619</v>
       </c>
       <c r="G10" t="n">
         <v>-5.714</v>
@@ -1234,13 +1234,13 @@
         <v>1.9474</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1221</v>
+        <v>1.3585</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3595</v>
+        <v>0.4864</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7626</v>
+        <v>0.8721</v>
       </c>
       <c r="V10" t="n">
         <v>2.1111</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8479</v>
+        <v>-4.6245</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1368</v>
+        <v>-0.9134</v>
       </c>
       <c r="F11" t="n">
         <v>-3.7111</v>
@@ -1312,10 +1312,10 @@
         <v>1.3632</v>
       </c>
       <c r="S11" t="n">
-        <v>0.275</v>
+        <v>0.4984</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0064</v>
+        <v>0.2169</v>
       </c>
       <c r="U11" t="n">
         <v>0.2815</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6168</v>
+        <v>-5.5728</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6913</v>
+        <v>1.5127</v>
       </c>
       <c r="F12" t="n">
-        <v>-7.3081</v>
+        <v>-7.0855</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0679</v>
@@ -1390,13 +1390,13 @@
         <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2489</v>
+        <v>-0.2049</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2367</v>
+        <v>-0.4153</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0122</v>
+        <v>0.2104</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2737</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.5241</v>
+        <v>-14.9057</v>
       </c>
       <c r="E13" t="n">
-        <v>12.5046</v>
+        <v>13.1228</v>
       </c>
       <c r="F13" t="n">
-        <v>-28.0286</v>
+        <v>-28.0287</v>
       </c>
       <c r="G13" t="n">
         <v>-19.2765</v>
@@ -1468,13 +1468,13 @@
         <v>12.658</v>
       </c>
       <c r="S13" t="n">
-        <v>2.750300000000001</v>
+        <v>3.3687</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2908000000000004</v>
+        <v>0.9093000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>2.4596</v>
+        <v>2.4595</v>
       </c>
       <c r="V13" t="n">
         <v>2.9494</v>
